--- a/artfynd/A 30921-2025 artfynd.xlsx
+++ b/artfynd/A 30921-2025 artfynd.xlsx
@@ -1787,7 +1787,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126503227</v>
+        <v>126503212</v>
       </c>
       <c r="B13" t="n">
         <v>57657</v>
@@ -1822,10 +1822,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>444290</v>
+        <v>444401</v>
       </c>
       <c r="R13" t="n">
-        <v>7037654</v>
+        <v>7037638</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1889,10 +1889,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126503217</v>
+        <v>126503235</v>
       </c>
       <c r="B14" t="n">
-        <v>57657</v>
+        <v>91259</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1900,21 +1900,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1924,10 +1924,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>444345</v>
+        <v>444601</v>
       </c>
       <c r="R14" t="n">
-        <v>7037688</v>
+        <v>7037789</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1960,11 +1960,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-07-07</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1991,7 +1986,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126503212</v>
+        <v>126503227</v>
       </c>
       <c r="B15" t="n">
         <v>57657</v>
@@ -2026,10 +2021,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>444401</v>
+        <v>444290</v>
       </c>
       <c r="R15" t="n">
-        <v>7037638</v>
+        <v>7037654</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2093,7 +2088,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126503208</v>
+        <v>126503217</v>
       </c>
       <c r="B16" t="n">
         <v>57657</v>
@@ -2128,10 +2123,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>444399</v>
+        <v>444345</v>
       </c>
       <c r="R16" t="n">
-        <v>7037782</v>
+        <v>7037688</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2195,10 +2190,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126503235</v>
+        <v>126503208</v>
       </c>
       <c r="B17" t="n">
-        <v>91259</v>
+        <v>57657</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2206,21 +2201,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2230,10 +2225,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>444601</v>
+        <v>444399</v>
       </c>
       <c r="R17" t="n">
-        <v>7037789</v>
+        <v>7037782</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2266,6 +2261,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -4740,7 +4740,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126503206</v>
+        <v>126503222</v>
       </c>
       <c r="B42" t="n">
         <v>57657</v>
@@ -4775,10 +4775,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>444445</v>
+        <v>444352</v>
       </c>
       <c r="R42" t="n">
-        <v>7037766</v>
+        <v>7037619</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4842,7 +4842,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126503222</v>
+        <v>126503202</v>
       </c>
       <c r="B43" t="n">
         <v>57657</v>
@@ -4877,10 +4877,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>444352</v>
+        <v>444431</v>
       </c>
       <c r="R43" t="n">
-        <v>7037619</v>
+        <v>7037579</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4917,7 +4917,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4944,7 +4944,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126503202</v>
+        <v>126503206</v>
       </c>
       <c r="B44" t="n">
         <v>57657</v>
@@ -4979,10 +4979,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>444431</v>
+        <v>444445</v>
       </c>
       <c r="R44" t="n">
-        <v>7037579</v>
+        <v>7037766</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">

--- a/artfynd/A 30921-2025 artfynd.xlsx
+++ b/artfynd/A 30921-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126503236</v>
+        <v>126503209</v>
       </c>
       <c r="B2" t="n">
-        <v>91263</v>
+        <v>57657</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>444461</v>
+        <v>444405</v>
       </c>
       <c r="R2" t="n">
-        <v>7037698</v>
+        <v>7037780</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -874,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126503209</v>
+        <v>126503236</v>
       </c>
       <c r="B4" t="n">
-        <v>57657</v>
+        <v>91263</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>444405</v>
+        <v>444461</v>
       </c>
       <c r="R4" t="n">
-        <v>7037780</v>
+        <v>7037698</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,11 +950,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-07-07</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1277,7 +1277,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126503194</v>
+        <v>126503231</v>
       </c>
       <c r="B8" t="n">
         <v>57657</v>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>444525</v>
+        <v>444550</v>
       </c>
       <c r="R8" t="n">
-        <v>7037707</v>
+        <v>7037828</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1379,7 +1379,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126503231</v>
+        <v>126503194</v>
       </c>
       <c r="B9" t="n">
         <v>57657</v>
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>444550</v>
+        <v>444525</v>
       </c>
       <c r="R9" t="n">
-        <v>7037828</v>
+        <v>7037707</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1787,10 +1787,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126503212</v>
+        <v>126503235</v>
       </c>
       <c r="B13" t="n">
-        <v>57657</v>
+        <v>91259</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1798,21 +1798,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1822,10 +1822,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>444401</v>
+        <v>444601</v>
       </c>
       <c r="R13" t="n">
-        <v>7037638</v>
+        <v>7037789</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1858,11 +1858,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-07-07</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1889,10 +1884,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126503235</v>
+        <v>126503217</v>
       </c>
       <c r="B14" t="n">
-        <v>91259</v>
+        <v>57657</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1900,21 +1895,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1924,10 +1919,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>444601</v>
+        <v>444345</v>
       </c>
       <c r="R14" t="n">
-        <v>7037789</v>
+        <v>7037688</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1960,6 +1955,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1986,7 +1986,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126503227</v>
+        <v>126503212</v>
       </c>
       <c r="B15" t="n">
         <v>57657</v>
@@ -2021,10 +2021,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>444290</v>
+        <v>444401</v>
       </c>
       <c r="R15" t="n">
-        <v>7037654</v>
+        <v>7037638</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2088,7 +2088,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126503217</v>
+        <v>126503208</v>
       </c>
       <c r="B16" t="n">
         <v>57657</v>
@@ -2123,10 +2123,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>444345</v>
+        <v>444399</v>
       </c>
       <c r="R16" t="n">
-        <v>7037688</v>
+        <v>7037782</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2190,7 +2190,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126503208</v>
+        <v>126503227</v>
       </c>
       <c r="B17" t="n">
         <v>57657</v>
@@ -2225,10 +2225,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>444399</v>
+        <v>444290</v>
       </c>
       <c r="R17" t="n">
-        <v>7037782</v>
+        <v>7037654</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2265,7 +2265,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2598,7 +2598,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126503223</v>
+        <v>126503232</v>
       </c>
       <c r="B21" t="n">
         <v>57657</v>
@@ -2633,10 +2633,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>444345</v>
+        <v>444558</v>
       </c>
       <c r="R21" t="n">
-        <v>7037606</v>
+        <v>7037773</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2700,7 +2700,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126503191</v>
+        <v>126503223</v>
       </c>
       <c r="B22" t="n">
         <v>57657</v>
@@ -2735,10 +2735,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>444558</v>
+        <v>444345</v>
       </c>
       <c r="R22" t="n">
-        <v>7037710</v>
+        <v>7037606</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2802,7 +2802,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126503232</v>
+        <v>126503191</v>
       </c>
       <c r="B23" t="n">
         <v>57657</v>
@@ -2840,7 +2840,7 @@
         <v>444558</v>
       </c>
       <c r="R23" t="n">
-        <v>7037773</v>
+        <v>7037710</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3006,10 +3006,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126503190</v>
+        <v>126503192</v>
       </c>
       <c r="B25" t="n">
-        <v>91245</v>
+        <v>57657</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3017,21 +3017,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3041,10 +3041,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>444576</v>
+        <v>444547</v>
       </c>
       <c r="R25" t="n">
-        <v>7037751</v>
+        <v>7037689</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3077,6 +3077,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3103,10 +3108,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126503189</v>
+        <v>126503238</v>
       </c>
       <c r="B26" t="n">
-        <v>91245</v>
+        <v>91263</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3114,21 +3119,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3138,10 +3143,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>444334</v>
+        <v>444416</v>
       </c>
       <c r="R26" t="n">
-        <v>7037735</v>
+        <v>7037767</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3200,10 +3205,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126503192</v>
+        <v>126503190</v>
       </c>
       <c r="B27" t="n">
-        <v>57657</v>
+        <v>91245</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3211,21 +3216,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3235,10 +3240,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>444547</v>
+        <v>444576</v>
       </c>
       <c r="R27" t="n">
-        <v>7037689</v>
+        <v>7037751</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3271,11 +3276,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-07-07</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3302,10 +3302,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126503197</v>
+        <v>126503189</v>
       </c>
       <c r="B28" t="n">
-        <v>57657</v>
+        <v>91245</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3313,21 +3313,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3337,10 +3337,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>444450</v>
+        <v>444334</v>
       </c>
       <c r="R28" t="n">
-        <v>7037573</v>
+        <v>7037735</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3373,11 +3373,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-07-07</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3404,10 +3399,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126503238</v>
+        <v>126503197</v>
       </c>
       <c r="B29" t="n">
-        <v>91263</v>
+        <v>57657</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3415,21 +3410,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3439,10 +3434,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>444416</v>
+        <v>444450</v>
       </c>
       <c r="R29" t="n">
-        <v>7037767</v>
+        <v>7037573</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3475,6 +3470,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3603,7 +3603,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126503233</v>
+        <v>126503224</v>
       </c>
       <c r="B31" t="n">
         <v>57657</v>
@@ -3638,10 +3638,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>444562</v>
+        <v>444344</v>
       </c>
       <c r="R31" t="n">
-        <v>7037745</v>
+        <v>7037609</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3678,7 +3678,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3705,7 +3705,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126503224</v>
+        <v>126503233</v>
       </c>
       <c r="B32" t="n">
         <v>57657</v>
@@ -3740,10 +3740,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>444344</v>
+        <v>444562</v>
       </c>
       <c r="R32" t="n">
-        <v>7037609</v>
+        <v>7037745</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3780,7 +3780,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4312,7 +4312,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126503228</v>
+        <v>126503195</v>
       </c>
       <c r="B38" t="n">
         <v>57657</v>
@@ -4340,37 +4340,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Hällberget vnv, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>444265</v>
+        <v>444488</v>
       </c>
       <c r="R38" t="n">
-        <v>7037666</v>
+        <v>7037674</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4407,7 +4387,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Skrämde upp hane och hona som befann sig på marknivå</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4434,7 +4414,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126503195</v>
+        <v>126503226</v>
       </c>
       <c r="B39" t="n">
         <v>57657</v>
@@ -4469,10 +4449,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>444488</v>
+        <v>444335</v>
       </c>
       <c r="R39" t="n">
-        <v>7037674</v>
+        <v>7037603</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4536,7 +4516,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126503226</v>
+        <v>126503228</v>
       </c>
       <c r="B40" t="n">
         <v>57657</v>
@@ -4564,17 +4544,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Hällberget vnv, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>444335</v>
+        <v>444265</v>
       </c>
       <c r="R40" t="n">
-        <v>7037603</v>
+        <v>7037666</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4611,7 +4611,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Skrämde upp hane och hona som befann sig på marknivå</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4740,7 +4740,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126503222</v>
+        <v>126503206</v>
       </c>
       <c r="B42" t="n">
         <v>57657</v>
@@ -4775,10 +4775,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>444352</v>
+        <v>444445</v>
       </c>
       <c r="R42" t="n">
-        <v>7037619</v>
+        <v>7037766</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4842,7 +4842,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126503202</v>
+        <v>126503222</v>
       </c>
       <c r="B43" t="n">
         <v>57657</v>
@@ -4877,10 +4877,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>444431</v>
+        <v>444352</v>
       </c>
       <c r="R43" t="n">
-        <v>7037579</v>
+        <v>7037619</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4917,7 +4917,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4944,7 +4944,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126503206</v>
+        <v>126503202</v>
       </c>
       <c r="B44" t="n">
         <v>57657</v>
@@ -4979,10 +4979,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>444445</v>
+        <v>444431</v>
       </c>
       <c r="R44" t="n">
-        <v>7037766</v>
+        <v>7037579</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">

--- a/artfynd/A 30921-2025 artfynd.xlsx
+++ b/artfynd/A 30921-2025 artfynd.xlsx
@@ -3603,7 +3603,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126503224</v>
+        <v>126503233</v>
       </c>
       <c r="B31" t="n">
         <v>57657</v>
@@ -3638,10 +3638,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>444344</v>
+        <v>444562</v>
       </c>
       <c r="R31" t="n">
-        <v>7037609</v>
+        <v>7037745</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3678,7 +3678,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3705,7 +3705,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126503233</v>
+        <v>126503224</v>
       </c>
       <c r="B32" t="n">
         <v>57657</v>
@@ -3740,10 +3740,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>444562</v>
+        <v>444344</v>
       </c>
       <c r="R32" t="n">
-        <v>7037745</v>
+        <v>7037609</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3780,7 +3780,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4312,7 +4312,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126503195</v>
+        <v>126503226</v>
       </c>
       <c r="B38" t="n">
         <v>57657</v>
@@ -4347,10 +4347,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>444488</v>
+        <v>444335</v>
       </c>
       <c r="R38" t="n">
-        <v>7037674</v>
+        <v>7037603</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4414,7 +4414,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126503226</v>
+        <v>126503228</v>
       </c>
       <c r="B39" t="n">
         <v>57657</v>
@@ -4442,17 +4442,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Hällberget vnv, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>444335</v>
+        <v>444265</v>
       </c>
       <c r="R39" t="n">
-        <v>7037603</v>
+        <v>7037666</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4489,7 +4509,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Skrämde upp hane och hona som befann sig på marknivå</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4516,7 +4536,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126503228</v>
+        <v>126503204</v>
       </c>
       <c r="B40" t="n">
         <v>57657</v>
@@ -4544,37 +4564,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Hällberget vnv, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>444265</v>
+        <v>444442</v>
       </c>
       <c r="R40" t="n">
-        <v>7037666</v>
+        <v>7037641</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4611,7 +4611,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Skrämde upp hane och hona som befann sig på marknivå</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4638,7 +4638,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126503204</v>
+        <v>126503195</v>
       </c>
       <c r="B41" t="n">
         <v>57657</v>
@@ -4673,10 +4673,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>444442</v>
+        <v>444488</v>
       </c>
       <c r="R41" t="n">
-        <v>7037641</v>
+        <v>7037674</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>

--- a/artfynd/A 30921-2025 artfynd.xlsx
+++ b/artfynd/A 30921-2025 artfynd.xlsx
@@ -976,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126503239</v>
+        <v>126503215</v>
       </c>
       <c r="B5" t="n">
-        <v>91263</v>
+        <v>57657</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,21 +987,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>444551</v>
+        <v>444383</v>
       </c>
       <c r="R5" t="n">
-        <v>7037829</v>
+        <v>7037614</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1047,6 +1047,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1073,7 +1078,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126503215</v>
+        <v>126503205</v>
       </c>
       <c r="B6" t="n">
         <v>57657</v>
@@ -1108,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>444383</v>
+        <v>444451</v>
       </c>
       <c r="R6" t="n">
-        <v>7037614</v>
+        <v>7037697</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1175,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126503205</v>
+        <v>126503239</v>
       </c>
       <c r="B7" t="n">
-        <v>57657</v>
+        <v>91263</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1186,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1210,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>444451</v>
+        <v>444551</v>
       </c>
       <c r="R7" t="n">
-        <v>7037697</v>
+        <v>7037829</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1246,11 +1251,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-07-07</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1884,7 +1884,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126503217</v>
+        <v>126503227</v>
       </c>
       <c r="B14" t="n">
         <v>57657</v>
@@ -1919,10 +1919,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>444345</v>
+        <v>444290</v>
       </c>
       <c r="R14" t="n">
-        <v>7037688</v>
+        <v>7037654</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1959,7 +1959,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1986,7 +1986,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126503212</v>
+        <v>126503217</v>
       </c>
       <c r="B15" t="n">
         <v>57657</v>
@@ -2021,10 +2021,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>444401</v>
+        <v>444345</v>
       </c>
       <c r="R15" t="n">
-        <v>7037638</v>
+        <v>7037688</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2061,7 +2061,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2088,7 +2088,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126503208</v>
+        <v>126503212</v>
       </c>
       <c r="B16" t="n">
         <v>57657</v>
@@ -2123,10 +2123,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>444399</v>
+        <v>444401</v>
       </c>
       <c r="R16" t="n">
-        <v>7037782</v>
+        <v>7037638</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2163,7 +2163,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2190,7 +2190,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126503227</v>
+        <v>126503208</v>
       </c>
       <c r="B17" t="n">
         <v>57657</v>
@@ -2225,10 +2225,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>444290</v>
+        <v>444399</v>
       </c>
       <c r="R17" t="n">
-        <v>7037654</v>
+        <v>7037782</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2265,7 +2265,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -3006,7 +3006,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126503192</v>
+        <v>126503197</v>
       </c>
       <c r="B25" t="n">
         <v>57657</v>
@@ -3041,10 +3041,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>444547</v>
+        <v>444450</v>
       </c>
       <c r="R25" t="n">
-        <v>7037689</v>
+        <v>7037573</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3108,10 +3108,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126503238</v>
+        <v>126503190</v>
       </c>
       <c r="B26" t="n">
-        <v>91263</v>
+        <v>91245</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3119,21 +3119,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3143,10 +3143,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>444416</v>
+        <v>444576</v>
       </c>
       <c r="R26" t="n">
-        <v>7037767</v>
+        <v>7037751</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3205,7 +3205,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126503190</v>
+        <v>126503189</v>
       </c>
       <c r="B27" t="n">
         <v>91245</v>
@@ -3240,10 +3240,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>444576</v>
+        <v>444334</v>
       </c>
       <c r="R27" t="n">
-        <v>7037751</v>
+        <v>7037735</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3302,10 +3302,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126503189</v>
+        <v>126503192</v>
       </c>
       <c r="B28" t="n">
-        <v>91245</v>
+        <v>57657</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3313,21 +3313,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3337,10 +3337,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>444334</v>
+        <v>444547</v>
       </c>
       <c r="R28" t="n">
-        <v>7037735</v>
+        <v>7037689</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3373,6 +3373,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3399,10 +3404,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126503197</v>
+        <v>126503238</v>
       </c>
       <c r="B29" t="n">
-        <v>57657</v>
+        <v>91263</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3410,21 +3415,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3434,10 +3439,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>444450</v>
+        <v>444416</v>
       </c>
       <c r="R29" t="n">
-        <v>7037573</v>
+        <v>7037767</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3470,11 +3475,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-07-07</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -5046,10 +5046,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126503213</v>
+        <v>126503234</v>
       </c>
       <c r="B45" t="n">
-        <v>57657</v>
+        <v>57654</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5057,16 +5057,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5081,10 +5081,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>444406</v>
+        <v>444631</v>
       </c>
       <c r="R45" t="n">
-        <v>7037634</v>
+        <v>7037796</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5121,7 +5121,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5148,10 +5148,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126503234</v>
+        <v>126503213</v>
       </c>
       <c r="B46" t="n">
-        <v>57654</v>
+        <v>57657</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5159,16 +5159,16 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5183,10 +5183,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>444631</v>
+        <v>444406</v>
       </c>
       <c r="R46" t="n">
-        <v>7037796</v>
+        <v>7037634</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5223,7 +5223,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 30921-2025 artfynd.xlsx
+++ b/artfynd/A 30921-2025 artfynd.xlsx
@@ -976,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126503215</v>
+        <v>126503239</v>
       </c>
       <c r="B5" t="n">
-        <v>57657</v>
+        <v>91263</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,21 +987,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>444383</v>
+        <v>444551</v>
       </c>
       <c r="R5" t="n">
-        <v>7037614</v>
+        <v>7037829</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1047,11 +1047,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-07-07</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1078,7 +1073,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126503205</v>
+        <v>126503215</v>
       </c>
       <c r="B6" t="n">
         <v>57657</v>
@@ -1113,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>444451</v>
+        <v>444383</v>
       </c>
       <c r="R6" t="n">
-        <v>7037697</v>
+        <v>7037614</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,10 +1175,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126503239</v>
+        <v>126503205</v>
       </c>
       <c r="B7" t="n">
-        <v>91263</v>
+        <v>57657</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,21 +1186,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>444551</v>
+        <v>444451</v>
       </c>
       <c r="R7" t="n">
-        <v>7037829</v>
+        <v>7037697</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1251,6 +1246,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -3006,7 +3006,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126503197</v>
+        <v>126503192</v>
       </c>
       <c r="B25" t="n">
         <v>57657</v>
@@ -3041,10 +3041,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>444450</v>
+        <v>444547</v>
       </c>
       <c r="R25" t="n">
-        <v>7037573</v>
+        <v>7037689</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3108,10 +3108,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126503190</v>
+        <v>126503238</v>
       </c>
       <c r="B26" t="n">
-        <v>91245</v>
+        <v>91263</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3119,21 +3119,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3143,10 +3143,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>444576</v>
+        <v>444416</v>
       </c>
       <c r="R26" t="n">
-        <v>7037751</v>
+        <v>7037767</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3205,7 +3205,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126503189</v>
+        <v>126503190</v>
       </c>
       <c r="B27" t="n">
         <v>91245</v>
@@ -3240,10 +3240,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>444334</v>
+        <v>444576</v>
       </c>
       <c r="R27" t="n">
-        <v>7037735</v>
+        <v>7037751</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3302,10 +3302,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126503192</v>
+        <v>126503189</v>
       </c>
       <c r="B28" t="n">
-        <v>57657</v>
+        <v>91245</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3313,21 +3313,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3337,10 +3337,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>444547</v>
+        <v>444334</v>
       </c>
       <c r="R28" t="n">
-        <v>7037689</v>
+        <v>7037735</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3373,11 +3373,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-07-07</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3404,10 +3399,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126503238</v>
+        <v>126503197</v>
       </c>
       <c r="B29" t="n">
-        <v>91263</v>
+        <v>57657</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3415,21 +3410,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3439,10 +3434,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>444416</v>
+        <v>444450</v>
       </c>
       <c r="R29" t="n">
-        <v>7037767</v>
+        <v>7037573</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3475,6 +3470,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-07-07</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 30921-2025 artfynd.xlsx
+++ b/artfynd/A 30921-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>126503218</v>
       </c>
       <c r="B3" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>126503209</v>
       </c>
       <c r="B4" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>126503205</v>
       </c>
       <c r="B5" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>126503215</v>
       </c>
       <c r="B6" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>126503231</v>
       </c>
       <c r="B8" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>126503194</v>
       </c>
       <c r="B9" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>126503196</v>
       </c>
       <c r="B10" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         <v>126503211</v>
       </c>
       <c r="B11" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>126503230</v>
       </c>
       <c r="B12" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>126503212</v>
       </c>
       <c r="B14" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         <v>126503217</v>
       </c>
       <c r="B15" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>126503227</v>
       </c>
       <c r="B16" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>126503208</v>
       </c>
       <c r="B17" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>126503229</v>
       </c>
       <c r="B18" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>126503207</v>
       </c>
       <c r="B19" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         <v>126503219</v>
       </c>
       <c r="B20" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>126503232</v>
       </c>
       <c r="B21" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>126503191</v>
       </c>
       <c r="B22" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>126503223</v>
       </c>
       <c r="B23" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
         <v>126503216</v>
       </c>
       <c r="B24" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         <v>126503192</v>
       </c>
       <c r="B25" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>126503197</v>
       </c>
       <c r="B29" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3504,7 +3504,7 @@
         <v>126503214</v>
       </c>
       <c r="B30" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         <v>126503224</v>
       </c>
       <c r="B31" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>126503233</v>
       </c>
       <c r="B32" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         <v>126503193</v>
       </c>
       <c r="B33" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4009,7 +4009,7 @@
         <v>126503225</v>
       </c>
       <c r="B35" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
         <v>126503201</v>
       </c>
       <c r="B36" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4213,7 +4213,7 @@
         <v>126503221</v>
       </c>
       <c r="B37" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         <v>126503226</v>
       </c>
       <c r="B38" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
         <v>126503204</v>
       </c>
       <c r="B39" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4519,7 +4519,7 @@
         <v>126503195</v>
       </c>
       <c r="B40" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
         <v>126503228</v>
       </c>
       <c r="B41" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>126503222</v>
       </c>
       <c r="B42" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>126503206</v>
       </c>
       <c r="B43" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>126503202</v>
       </c>
       <c r="B44" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         <v>126503213</v>
       </c>
       <c r="B45" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 30921-2025 artfynd.xlsx
+++ b/artfynd/A 30921-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>126503218</v>
       </c>
       <c r="B3" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>126503209</v>
       </c>
       <c r="B4" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>126503205</v>
       </c>
       <c r="B5" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>126503215</v>
       </c>
       <c r="B6" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>126503231</v>
       </c>
       <c r="B8" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>126503194</v>
       </c>
       <c r="B9" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>126503196</v>
       </c>
       <c r="B10" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         <v>126503211</v>
       </c>
       <c r="B11" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>126503230</v>
       </c>
       <c r="B12" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>126503212</v>
       </c>
       <c r="B14" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         <v>126503217</v>
       </c>
       <c r="B15" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>126503227</v>
       </c>
       <c r="B16" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>126503208</v>
       </c>
       <c r="B17" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>126503229</v>
       </c>
       <c r="B18" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>126503207</v>
       </c>
       <c r="B19" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         <v>126503219</v>
       </c>
       <c r="B20" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>126503232</v>
       </c>
       <c r="B21" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>126503191</v>
       </c>
       <c r="B22" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>126503223</v>
       </c>
       <c r="B23" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
         <v>126503216</v>
       </c>
       <c r="B24" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         <v>126503192</v>
       </c>
       <c r="B25" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>126503197</v>
       </c>
       <c r="B29" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3504,7 +3504,7 @@
         <v>126503214</v>
       </c>
       <c r="B30" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         <v>126503224</v>
       </c>
       <c r="B31" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>126503233</v>
       </c>
       <c r="B32" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         <v>126503193</v>
       </c>
       <c r="B33" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4009,7 +4009,7 @@
         <v>126503225</v>
       </c>
       <c r="B35" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
         <v>126503201</v>
       </c>
       <c r="B36" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4213,7 +4213,7 @@
         <v>126503221</v>
       </c>
       <c r="B37" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         <v>126503226</v>
       </c>
       <c r="B38" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
         <v>126503204</v>
       </c>
       <c r="B39" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4519,7 +4519,7 @@
         <v>126503195</v>
       </c>
       <c r="B40" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
         <v>126503228</v>
       </c>
       <c r="B41" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>126503222</v>
       </c>
       <c r="B42" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>126503206</v>
       </c>
       <c r="B43" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>126503202</v>
       </c>
       <c r="B44" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         <v>126503213</v>
       </c>
       <c r="B45" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 30921-2025 artfynd.xlsx
+++ b/artfynd/A 30921-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>126503218</v>
       </c>
       <c r="B3" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>126503209</v>
       </c>
       <c r="B4" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>126503205</v>
       </c>
       <c r="B5" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>126503215</v>
       </c>
       <c r="B6" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>126503231</v>
       </c>
       <c r="B8" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>126503194</v>
       </c>
       <c r="B9" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>126503196</v>
       </c>
       <c r="B10" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         <v>126503211</v>
       </c>
       <c r="B11" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>126503230</v>
       </c>
       <c r="B12" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>126503212</v>
       </c>
       <c r="B14" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         <v>126503217</v>
       </c>
       <c r="B15" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>126503227</v>
       </c>
       <c r="B16" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>126503208</v>
       </c>
       <c r="B17" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>126503229</v>
       </c>
       <c r="B18" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>126503207</v>
       </c>
       <c r="B19" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         <v>126503219</v>
       </c>
       <c r="B20" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>126503232</v>
       </c>
       <c r="B21" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>126503191</v>
       </c>
       <c r="B22" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>126503223</v>
       </c>
       <c r="B23" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
         <v>126503216</v>
       </c>
       <c r="B24" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         <v>126503192</v>
       </c>
       <c r="B25" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>126503197</v>
       </c>
       <c r="B29" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3504,7 +3504,7 @@
         <v>126503214</v>
       </c>
       <c r="B30" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         <v>126503224</v>
       </c>
       <c r="B31" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>126503233</v>
       </c>
       <c r="B32" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         <v>126503193</v>
       </c>
       <c r="B33" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4009,7 +4009,7 @@
         <v>126503225</v>
       </c>
       <c r="B35" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
         <v>126503201</v>
       </c>
       <c r="B36" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4213,7 +4213,7 @@
         <v>126503221</v>
       </c>
       <c r="B37" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         <v>126503226</v>
       </c>
       <c r="B38" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
         <v>126503204</v>
       </c>
       <c r="B39" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4519,7 +4519,7 @@
         <v>126503195</v>
       </c>
       <c r="B40" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
         <v>126503228</v>
       </c>
       <c r="B41" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>126503222</v>
       </c>
       <c r="B42" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>126503206</v>
       </c>
       <c r="B43" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>126503202</v>
       </c>
       <c r="B44" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         <v>126503213</v>
       </c>
       <c r="B45" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 30921-2025 artfynd.xlsx
+++ b/artfynd/A 30921-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>126503218</v>
       </c>
       <c r="B3" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>126503209</v>
       </c>
       <c r="B4" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>126503205</v>
       </c>
       <c r="B5" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>126503215</v>
       </c>
       <c r="B6" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>126503231</v>
       </c>
       <c r="B8" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>126503194</v>
       </c>
       <c r="B9" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>126503196</v>
       </c>
       <c r="B10" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         <v>126503211</v>
       </c>
       <c r="B11" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>126503230</v>
       </c>
       <c r="B12" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>126503212</v>
       </c>
       <c r="B14" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         <v>126503217</v>
       </c>
       <c r="B15" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>126503227</v>
       </c>
       <c r="B16" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>126503208</v>
       </c>
       <c r="B17" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>126503229</v>
       </c>
       <c r="B18" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>126503207</v>
       </c>
       <c r="B19" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         <v>126503219</v>
       </c>
       <c r="B20" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>126503232</v>
       </c>
       <c r="B21" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>126503191</v>
       </c>
       <c r="B22" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>126503223</v>
       </c>
       <c r="B23" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
         <v>126503216</v>
       </c>
       <c r="B24" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         <v>126503192</v>
       </c>
       <c r="B25" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>126503197</v>
       </c>
       <c r="B29" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3504,7 +3504,7 @@
         <v>126503214</v>
       </c>
       <c r="B30" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         <v>126503224</v>
       </c>
       <c r="B31" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         <v>126503233</v>
       </c>
       <c r="B32" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         <v>126503193</v>
       </c>
       <c r="B33" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4009,7 +4009,7 @@
         <v>126503225</v>
       </c>
       <c r="B35" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
         <v>126503201</v>
       </c>
       <c r="B36" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4213,7 +4213,7 @@
         <v>126503221</v>
       </c>
       <c r="B37" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         <v>126503226</v>
       </c>
       <c r="B38" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
         <v>126503204</v>
       </c>
       <c r="B39" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4519,7 +4519,7 @@
         <v>126503195</v>
       </c>
       <c r="B40" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
         <v>126503228</v>
       </c>
       <c r="B41" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>126503222</v>
       </c>
       <c r="B42" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>126503206</v>
       </c>
       <c r="B43" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>126503202</v>
       </c>
       <c r="B44" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         <v>126503213</v>
       </c>
       <c r="B45" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 30921-2025 artfynd.xlsx
+++ b/artfynd/A 30921-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY46"/>
+  <dimension ref="A1:AY56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5248,6 +5248,1023 @@
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>129562901</v>
+      </c>
+      <c r="B47" t="n">
+        <v>80150</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Naturskog söder om Kaxås, Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>444511</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7037681</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>Friskt, örtrikt bäckdråg i grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>129562897</v>
+      </c>
+      <c r="B48" t="n">
+        <v>91570</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Naturskog söder om Kaxås, Jmt</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>444374</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7037756</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>Flerskiktad och olikåldrig grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>129562905</v>
+      </c>
+      <c r="B49" t="n">
+        <v>91550</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Naturskog söder om Kaxås, Jmt</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>444381</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7037739</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>Kalpåverkat fuktstråk</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>129562900</v>
+      </c>
+      <c r="B50" t="n">
+        <v>80149</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Naturskog söder om Kaxås, Jmt</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>444511</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7037681</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>Friskt, örtrikt bäckdråg i grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>129562906</v>
+      </c>
+      <c r="B51" t="n">
+        <v>83012</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Naturskog söder om Kaxås, Jmt</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>444395</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7037758</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>Kalpåverkat fuktstråk</t>
+        </is>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>129562903</v>
+      </c>
+      <c r="B52" t="n">
+        <v>91570</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Naturskog söder om Kaxås, Jmt</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>444354</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7037634</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>Flerskiktad och olikåldrig grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>129562896</v>
+      </c>
+      <c r="B53" t="n">
+        <v>91570</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Naturskog söder om Kaxås, Jmt</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>444598</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7037765</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>Flerskiktad och olikåldrig grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>129562898</v>
+      </c>
+      <c r="B54" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Naturskog söder om Kaxås, Jmt</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>444587</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7037780</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>Flerskiktad och olikåldrig grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>129562899</v>
+      </c>
+      <c r="B55" t="n">
+        <v>88801</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>4405</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Diskvaxskivling</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Hygrophorus discoideus</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Pers.) Fr.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Naturskog söder om Kaxås, Jmt</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>444542</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7037818</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>Friskt, örtrikt bäckdråg i grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>129562902</v>
+      </c>
+      <c r="B56" t="n">
+        <v>91070</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>256335</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Taggfingersvamp</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Ramaria karstenii</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Sacc. &amp; P.Syd.) Corner</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Naturskog söder om Kaxås, Jmt</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>444503</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7037709</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Trötta och bleknade fruktkroppar men tydligt ljusbruna, svag doft och smak och relativt stora, mykorrhizabildande i lämplig miljö. Växte i en mindre häxring.</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>Friskt, örtrikt bäckdråg i grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30921-2025 artfynd.xlsx
+++ b/artfynd/A 30921-2025 artfynd.xlsx
@@ -5355,7 +5355,7 @@
         <v>129562897</v>
       </c>
       <c r="B48" t="n">
-        <v>91570</v>
+        <v>91573</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5453,7 +5453,7 @@
         <v>129562905</v>
       </c>
       <c r="B49" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5552,10 +5552,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129562900</v>
+        <v>129562906</v>
       </c>
       <c r="B50" t="n">
-        <v>80149</v>
+        <v>83012</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5563,21 +5563,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5587,10 +5587,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>444511</v>
+        <v>444395</v>
       </c>
       <c r="R50" t="n">
-        <v>7037681</v>
+        <v>7037758</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5636,7 +5636,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Friskt, örtrikt bäckdråg i grannaturskog</t>
+          <t>Kalpåverkat fuktstråk</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -5654,10 +5654,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129562906</v>
+        <v>129562900</v>
       </c>
       <c r="B51" t="n">
-        <v>83012</v>
+        <v>80149</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5665,21 +5665,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5689,10 +5689,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>444395</v>
+        <v>444511</v>
       </c>
       <c r="R51" t="n">
-        <v>7037758</v>
+        <v>7037681</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>Kalpåverkat fuktstråk</t>
+          <t>Friskt, örtrikt bäckdråg i grannaturskog</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -5759,7 +5759,7 @@
         <v>129562903</v>
       </c>
       <c r="B52" t="n">
-        <v>91570</v>
+        <v>91573</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>129562896</v>
       </c>
       <c r="B53" t="n">
-        <v>91570</v>
+        <v>91573</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6159,7 +6159,7 @@
         <v>129562902</v>
       </c>
       <c r="B56" t="n">
-        <v>91070</v>
+        <v>91073</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 30921-2025 artfynd.xlsx
+++ b/artfynd/A 30921-2025 artfynd.xlsx
@@ -5250,10 +5250,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129562901</v>
+        <v>129562897</v>
       </c>
       <c r="B47" t="n">
-        <v>80150</v>
+        <v>91573</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5261,23 +5261,19 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5285,10 +5281,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>444511</v>
+        <v>444374</v>
       </c>
       <c r="R47" t="n">
-        <v>7037681</v>
+        <v>7037756</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5334,7 +5330,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>Friskt, örtrikt bäckdråg i grannaturskog</t>
+          <t>Flerskiktad och olikåldrig grannaturskog</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -5352,10 +5348,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129562897</v>
+        <v>129562901</v>
       </c>
       <c r="B48" t="n">
-        <v>91573</v>
+        <v>80150</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5363,19 +5359,23 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5383,10 +5383,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>444374</v>
+        <v>444511</v>
       </c>
       <c r="R48" t="n">
-        <v>7037756</v>
+        <v>7037681</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Flerskiktad och olikåldrig grannaturskog</t>
+          <t>Friskt, örtrikt bäckdråg i grannaturskog</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -5552,10 +5552,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129562906</v>
+        <v>129562900</v>
       </c>
       <c r="B50" t="n">
-        <v>83012</v>
+        <v>80149</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5563,21 +5563,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5587,10 +5587,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>444395</v>
+        <v>444511</v>
       </c>
       <c r="R50" t="n">
-        <v>7037758</v>
+        <v>7037681</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5636,7 +5636,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Kalpåverkat fuktstråk</t>
+          <t>Friskt, örtrikt bäckdråg i grannaturskog</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -5654,10 +5654,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129562900</v>
+        <v>129562906</v>
       </c>
       <c r="B51" t="n">
-        <v>80149</v>
+        <v>83012</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5665,21 +5665,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5689,10 +5689,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>444511</v>
+        <v>444395</v>
       </c>
       <c r="R51" t="n">
-        <v>7037681</v>
+        <v>7037758</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>Friskt, örtrikt bäckdråg i grannaturskog</t>
+          <t>Kalpåverkat fuktstråk</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -5952,32 +5952,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129562898</v>
+        <v>129562899</v>
       </c>
       <c r="B54" t="n">
-        <v>79044</v>
+        <v>88801</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>4405</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5987,10 +5987,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>444587</v>
+        <v>444542</v>
       </c>
       <c r="R54" t="n">
-        <v>7037780</v>
+        <v>7037818</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6036,7 +6036,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>Flerskiktad och olikåldrig grannaturskog</t>
+          <t>Friskt, örtrikt bäckdråg i grannaturskog</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6054,32 +6054,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129562899</v>
+        <v>129562898</v>
       </c>
       <c r="B55" t="n">
-        <v>88801</v>
+        <v>79044</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4405</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6089,10 +6089,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>444542</v>
+        <v>444587</v>
       </c>
       <c r="R55" t="n">
-        <v>7037818</v>
+        <v>7037780</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>Friskt, örtrikt bäckdråg i grannaturskog</t>
+          <t>Flerskiktad och olikåldrig grannaturskog</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>

--- a/artfynd/A 30921-2025 artfynd.xlsx
+++ b/artfynd/A 30921-2025 artfynd.xlsx
@@ -5952,32 +5952,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129562899</v>
+        <v>129562898</v>
       </c>
       <c r="B54" t="n">
-        <v>88801</v>
+        <v>79044</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4405</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5987,10 +5987,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>444542</v>
+        <v>444587</v>
       </c>
       <c r="R54" t="n">
-        <v>7037818</v>
+        <v>7037780</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6036,7 +6036,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>Friskt, örtrikt bäckdråg i grannaturskog</t>
+          <t>Flerskiktad och olikåldrig grannaturskog</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6054,32 +6054,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129562898</v>
+        <v>129562899</v>
       </c>
       <c r="B55" t="n">
-        <v>79044</v>
+        <v>88801</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>4405</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6089,10 +6089,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>444587</v>
+        <v>444542</v>
       </c>
       <c r="R55" t="n">
-        <v>7037780</v>
+        <v>7037818</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>Flerskiktad och olikåldrig grannaturskog</t>
+          <t>Friskt, örtrikt bäckdråg i grannaturskog</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>

--- a/artfynd/A 30921-2025 artfynd.xlsx
+++ b/artfynd/A 30921-2025 artfynd.xlsx
@@ -5552,10 +5552,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129562900</v>
+        <v>129562906</v>
       </c>
       <c r="B50" t="n">
-        <v>80149</v>
+        <v>83012</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5563,21 +5563,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5587,10 +5587,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>444511</v>
+        <v>444395</v>
       </c>
       <c r="R50" t="n">
-        <v>7037681</v>
+        <v>7037758</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5636,7 +5636,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Friskt, örtrikt bäckdråg i grannaturskog</t>
+          <t>Kalpåverkat fuktstråk</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -5654,10 +5654,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129562906</v>
+        <v>129562900</v>
       </c>
       <c r="B51" t="n">
-        <v>83012</v>
+        <v>80149</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5665,21 +5665,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5689,10 +5689,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>444395</v>
+        <v>444511</v>
       </c>
       <c r="R51" t="n">
-        <v>7037758</v>
+        <v>7037681</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>Kalpåverkat fuktstråk</t>
+          <t>Friskt, örtrikt bäckdråg i grannaturskog</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -5952,32 +5952,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129562898</v>
+        <v>129562899</v>
       </c>
       <c r="B54" t="n">
-        <v>79044</v>
+        <v>88801</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>4405</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5987,10 +5987,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>444587</v>
+        <v>444542</v>
       </c>
       <c r="R54" t="n">
-        <v>7037780</v>
+        <v>7037818</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6036,7 +6036,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>Flerskiktad och olikåldrig grannaturskog</t>
+          <t>Friskt, örtrikt bäckdråg i grannaturskog</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6054,32 +6054,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129562899</v>
+        <v>129562898</v>
       </c>
       <c r="B55" t="n">
-        <v>88801</v>
+        <v>79044</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4405</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6089,10 +6089,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>444542</v>
+        <v>444587</v>
       </c>
       <c r="R55" t="n">
-        <v>7037818</v>
+        <v>7037780</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>Friskt, örtrikt bäckdråg i grannaturskog</t>
+          <t>Flerskiktad och olikåldrig grannaturskog</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>

--- a/artfynd/A 30921-2025 artfynd.xlsx
+++ b/artfynd/A 30921-2025 artfynd.xlsx
@@ -5250,10 +5250,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129562897</v>
+        <v>129562901</v>
       </c>
       <c r="B47" t="n">
-        <v>91573</v>
+        <v>80150</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5261,19 +5261,23 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr"/>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5281,10 +5285,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>444374</v>
+        <v>444511</v>
       </c>
       <c r="R47" t="n">
-        <v>7037756</v>
+        <v>7037681</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5330,7 +5334,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>Flerskiktad och olikåldrig grannaturskog</t>
+          <t>Friskt, örtrikt bäckdråg i grannaturskog</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -5348,10 +5352,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129562901</v>
+        <v>129562897</v>
       </c>
       <c r="B48" t="n">
-        <v>80150</v>
+        <v>91573</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5359,23 +5363,19 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5383,10 +5383,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>444511</v>
+        <v>444374</v>
       </c>
       <c r="R48" t="n">
-        <v>7037681</v>
+        <v>7037756</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Friskt, örtrikt bäckdråg i grannaturskog</t>
+          <t>Flerskiktad och olikåldrig grannaturskog</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -5552,10 +5552,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129562906</v>
+        <v>129562900</v>
       </c>
       <c r="B50" t="n">
-        <v>83012</v>
+        <v>80149</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5563,21 +5563,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5587,10 +5587,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>444395</v>
+        <v>444511</v>
       </c>
       <c r="R50" t="n">
-        <v>7037758</v>
+        <v>7037681</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5636,7 +5636,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Kalpåverkat fuktstråk</t>
+          <t>Friskt, örtrikt bäckdråg i grannaturskog</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -5654,10 +5654,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129562900</v>
+        <v>129562906</v>
       </c>
       <c r="B51" t="n">
-        <v>80149</v>
+        <v>83012</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5665,21 +5665,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5689,10 +5689,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>444511</v>
+        <v>444395</v>
       </c>
       <c r="R51" t="n">
-        <v>7037681</v>
+        <v>7037758</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>Friskt, örtrikt bäckdråg i grannaturskog</t>
+          <t>Kalpåverkat fuktstråk</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>

--- a/artfynd/A 30921-2025 artfynd.xlsx
+++ b/artfynd/A 30921-2025 artfynd.xlsx
@@ -5552,10 +5552,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129562900</v>
+        <v>129562906</v>
       </c>
       <c r="B50" t="n">
-        <v>80149</v>
+        <v>83012</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5563,21 +5563,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5587,10 +5587,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>444511</v>
+        <v>444395</v>
       </c>
       <c r="R50" t="n">
-        <v>7037681</v>
+        <v>7037758</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5636,7 +5636,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Friskt, örtrikt bäckdråg i grannaturskog</t>
+          <t>Kalpåverkat fuktstråk</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -5654,10 +5654,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129562906</v>
+        <v>129562900</v>
       </c>
       <c r="B51" t="n">
-        <v>83012</v>
+        <v>80149</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5665,21 +5665,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5689,10 +5689,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>444395</v>
+        <v>444511</v>
       </c>
       <c r="R51" t="n">
-        <v>7037758</v>
+        <v>7037681</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>Kalpåverkat fuktstråk</t>
+          <t>Friskt, örtrikt bäckdråg i grannaturskog</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -5952,32 +5952,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129562899</v>
+        <v>129562898</v>
       </c>
       <c r="B54" t="n">
-        <v>88801</v>
+        <v>79044</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4405</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5987,10 +5987,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>444542</v>
+        <v>444587</v>
       </c>
       <c r="R54" t="n">
-        <v>7037818</v>
+        <v>7037780</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6036,7 +6036,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>Friskt, örtrikt bäckdråg i grannaturskog</t>
+          <t>Flerskiktad och olikåldrig grannaturskog</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6054,32 +6054,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129562898</v>
+        <v>129562899</v>
       </c>
       <c r="B55" t="n">
-        <v>79044</v>
+        <v>88801</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>4405</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6089,10 +6089,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>444587</v>
+        <v>444542</v>
       </c>
       <c r="R55" t="n">
-        <v>7037780</v>
+        <v>7037818</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>Flerskiktad och olikåldrig grannaturskog</t>
+          <t>Friskt, örtrikt bäckdråg i grannaturskog</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>

--- a/artfynd/A 30921-2025 artfynd.xlsx
+++ b/artfynd/A 30921-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY56"/>
+  <dimension ref="A1:AY55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5253,7 +5253,7 @@
         <v>129562901</v>
       </c>
       <c r="B47" t="n">
-        <v>80150</v>
+        <v>80176</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
         <v>129562897</v>
       </c>
       <c r="B48" t="n">
-        <v>91573</v>
+        <v>91601</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5453,7 +5453,7 @@
         <v>129562905</v>
       </c>
       <c r="B49" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>129562906</v>
       </c>
       <c r="B50" t="n">
-        <v>83012</v>
+        <v>83039</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         <v>129562900</v>
       </c>
       <c r="B51" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         <v>129562903</v>
       </c>
       <c r="B52" t="n">
-        <v>91573</v>
+        <v>91601</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>129562896</v>
       </c>
       <c r="B53" t="n">
-        <v>91573</v>
+        <v>91601</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5952,32 +5952,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129562898</v>
+        <v>129562899</v>
       </c>
       <c r="B54" t="n">
-        <v>79044</v>
+        <v>88829</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>4405</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5987,10 +5987,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>444587</v>
+        <v>444542</v>
       </c>
       <c r="R54" t="n">
-        <v>7037780</v>
+        <v>7037818</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6036,7 +6036,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>Flerskiktad och olikåldrig grannaturskog</t>
+          <t>Friskt, örtrikt bäckdråg i grannaturskog</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6054,32 +6054,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129562899</v>
+        <v>129562898</v>
       </c>
       <c r="B55" t="n">
-        <v>88801</v>
+        <v>79070</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4405</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6089,10 +6089,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>444542</v>
+        <v>444587</v>
       </c>
       <c r="R55" t="n">
-        <v>7037818</v>
+        <v>7037780</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>Friskt, örtrikt bäckdråg i grannaturskog</t>
+          <t>Flerskiktad och olikåldrig grannaturskog</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -6153,117 +6153,6 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>129562902</v>
-      </c>
-      <c r="B56" t="n">
-        <v>91073</v>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E56" t="n">
-        <v>256335</v>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Taggfingersvamp</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Ramaria karstenii</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>(Sacc. &amp; P.Syd.) Corner</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>Naturskog söder om Kaxås, Jmt</t>
-        </is>
-      </c>
-      <c r="Q56" t="n">
-        <v>444503</v>
-      </c>
-      <c r="R56" t="n">
-        <v>7037709</v>
-      </c>
-      <c r="S56" t="n">
-        <v>10</v>
-      </c>
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W56" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y56" t="inlineStr">
-        <is>
-          <t>2025-11-06</t>
-        </is>
-      </c>
-      <c r="AA56" t="inlineStr">
-        <is>
-          <t>2025-11-06</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Trötta och bleknade fruktkroppar men tydligt ljusbruna, svag doft och smak och relativt stora, mykorrhizabildande i lämplig miljö. Växte i en mindre häxring.</t>
-        </is>
-      </c>
-      <c r="AD56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF56" t="inlineStr"/>
-      <c r="AG56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI56" t="inlineStr">
-        <is>
-          <t>Friskt, örtrikt bäckdråg i grannaturskog</t>
-        </is>
-      </c>
-      <c r="AT56" t="inlineStr"/>
-      <c r="AW56" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30921-2025 artfynd.xlsx
+++ b/artfynd/A 30921-2025 artfynd.xlsx
@@ -5253,7 +5253,7 @@
         <v>129562901</v>
       </c>
       <c r="B47" t="n">
-        <v>80176</v>
+        <v>80181</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
         <v>129562897</v>
       </c>
       <c r="B48" t="n">
-        <v>91601</v>
+        <v>91607</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5453,7 +5453,7 @@
         <v>129562905</v>
       </c>
       <c r="B49" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>129562906</v>
       </c>
       <c r="B50" t="n">
-        <v>83039</v>
+        <v>83044</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         <v>129562900</v>
       </c>
       <c r="B51" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         <v>129562903</v>
       </c>
       <c r="B52" t="n">
-        <v>91601</v>
+        <v>91607</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>129562896</v>
       </c>
       <c r="B53" t="n">
-        <v>91601</v>
+        <v>91607</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         <v>129562899</v>
       </c>
       <c r="B54" t="n">
-        <v>88829</v>
+        <v>88835</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6057,7 +6057,7 @@
         <v>129562898</v>
       </c>
       <c r="B55" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 30921-2025 artfynd.xlsx
+++ b/artfynd/A 30921-2025 artfynd.xlsx
@@ -5253,7 +5253,7 @@
         <v>129562901</v>
       </c>
       <c r="B47" t="n">
-        <v>80181</v>
+        <v>80182</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
         <v>129562897</v>
       </c>
       <c r="B48" t="n">
-        <v>91607</v>
+        <v>91608</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5453,7 +5453,7 @@
         <v>129562905</v>
       </c>
       <c r="B49" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>129562906</v>
       </c>
       <c r="B50" t="n">
-        <v>83044</v>
+        <v>83045</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         <v>129562900</v>
       </c>
       <c r="B51" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5756,10 +5756,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129562903</v>
+        <v>129562896</v>
       </c>
       <c r="B52" t="n">
-        <v>91607</v>
+        <v>91608</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5787,10 +5787,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>444354</v>
+        <v>444598</v>
       </c>
       <c r="R52" t="n">
-        <v>7037634</v>
+        <v>7037765</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5854,10 +5854,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129562896</v>
+        <v>129562903</v>
       </c>
       <c r="B53" t="n">
-        <v>91607</v>
+        <v>91608</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5885,10 +5885,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>444598</v>
+        <v>444354</v>
       </c>
       <c r="R53" t="n">
-        <v>7037765</v>
+        <v>7037634</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5955,7 +5955,7 @@
         <v>129562899</v>
       </c>
       <c r="B54" t="n">
-        <v>88835</v>
+        <v>88836</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6057,7 +6057,7 @@
         <v>129562898</v>
       </c>
       <c r="B55" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 30921-2025 artfynd.xlsx
+++ b/artfynd/A 30921-2025 artfynd.xlsx
@@ -5552,10 +5552,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129562906</v>
+        <v>129562900</v>
       </c>
       <c r="B50" t="n">
-        <v>83045</v>
+        <v>80181</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5563,21 +5563,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5587,10 +5587,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>444395</v>
+        <v>444511</v>
       </c>
       <c r="R50" t="n">
-        <v>7037758</v>
+        <v>7037681</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5636,7 +5636,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Kalpåverkat fuktstråk</t>
+          <t>Friskt, örtrikt bäckdråg i grannaturskog</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -5654,10 +5654,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129562900</v>
+        <v>129562906</v>
       </c>
       <c r="B51" t="n">
-        <v>80181</v>
+        <v>83045</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5665,21 +5665,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5689,10 +5689,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>444511</v>
+        <v>444395</v>
       </c>
       <c r="R51" t="n">
-        <v>7037681</v>
+        <v>7037758</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>Friskt, örtrikt bäckdråg i grannaturskog</t>
+          <t>Kalpåverkat fuktstråk</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>

--- a/artfynd/A 30921-2025 artfynd.xlsx
+++ b/artfynd/A 30921-2025 artfynd.xlsx
@@ -5250,10 +5250,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129562901</v>
+        <v>129562897</v>
       </c>
       <c r="B47" t="n">
-        <v>80182</v>
+        <v>91613</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5261,23 +5261,19 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5285,10 +5281,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>444511</v>
+        <v>444374</v>
       </c>
       <c r="R47" t="n">
-        <v>7037681</v>
+        <v>7037756</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5334,7 +5330,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>Friskt, örtrikt bäckdråg i grannaturskog</t>
+          <t>Flerskiktad och olikåldrig grannaturskog</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -5352,10 +5348,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129562897</v>
+        <v>129562901</v>
       </c>
       <c r="B48" t="n">
-        <v>91608</v>
+        <v>80187</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5363,19 +5359,23 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5383,10 +5383,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>444374</v>
+        <v>444511</v>
       </c>
       <c r="R48" t="n">
-        <v>7037756</v>
+        <v>7037681</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Flerskiktad och olikåldrig grannaturskog</t>
+          <t>Friskt, örtrikt bäckdråg i grannaturskog</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -5453,7 +5453,7 @@
         <v>129562905</v>
       </c>
       <c r="B49" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5552,10 +5552,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129562900</v>
+        <v>129562906</v>
       </c>
       <c r="B50" t="n">
-        <v>80181</v>
+        <v>83050</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5563,21 +5563,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5587,10 +5587,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>444511</v>
+        <v>444395</v>
       </c>
       <c r="R50" t="n">
-        <v>7037681</v>
+        <v>7037758</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5636,7 +5636,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Friskt, örtrikt bäckdråg i grannaturskog</t>
+          <t>Kalpåverkat fuktstråk</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -5654,10 +5654,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129562906</v>
+        <v>129562900</v>
       </c>
       <c r="B51" t="n">
-        <v>83045</v>
+        <v>80186</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5665,21 +5665,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5689,10 +5689,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>444395</v>
+        <v>444511</v>
       </c>
       <c r="R51" t="n">
-        <v>7037758</v>
+        <v>7037681</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>Kalpåverkat fuktstråk</t>
+          <t>Friskt, örtrikt bäckdråg i grannaturskog</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -5756,10 +5756,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129562896</v>
+        <v>129562903</v>
       </c>
       <c r="B52" t="n">
-        <v>91608</v>
+        <v>91613</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5787,10 +5787,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>444598</v>
+        <v>444354</v>
       </c>
       <c r="R52" t="n">
-        <v>7037765</v>
+        <v>7037634</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5854,10 +5854,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129562903</v>
+        <v>129562896</v>
       </c>
       <c r="B53" t="n">
-        <v>91608</v>
+        <v>91613</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5885,10 +5885,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>444354</v>
+        <v>444598</v>
       </c>
       <c r="R53" t="n">
-        <v>7037634</v>
+        <v>7037765</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5955,7 +5955,7 @@
         <v>129562899</v>
       </c>
       <c r="B54" t="n">
-        <v>88836</v>
+        <v>88841</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6057,7 +6057,7 @@
         <v>129562898</v>
       </c>
       <c r="B55" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 30921-2025 artfynd.xlsx
+++ b/artfynd/A 30921-2025 artfynd.xlsx
@@ -5952,32 +5952,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129562899</v>
+        <v>129562898</v>
       </c>
       <c r="B54" t="n">
-        <v>88841</v>
+        <v>79081</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4405</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5987,10 +5987,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>444542</v>
+        <v>444587</v>
       </c>
       <c r="R54" t="n">
-        <v>7037818</v>
+        <v>7037780</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6036,7 +6036,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>Friskt, örtrikt bäckdråg i grannaturskog</t>
+          <t>Flerskiktad och olikåldrig grannaturskog</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6054,32 +6054,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129562898</v>
+        <v>129562899</v>
       </c>
       <c r="B55" t="n">
-        <v>79081</v>
+        <v>88841</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>4405</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6089,10 +6089,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>444587</v>
+        <v>444542</v>
       </c>
       <c r="R55" t="n">
-        <v>7037780</v>
+        <v>7037818</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>Flerskiktad och olikåldrig grannaturskog</t>
+          <t>Friskt, örtrikt bäckdråg i grannaturskog</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>

--- a/artfynd/A 30921-2025 artfynd.xlsx
+++ b/artfynd/A 30921-2025 artfynd.xlsx
@@ -5250,10 +5250,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129562897</v>
+        <v>129562901</v>
       </c>
       <c r="B47" t="n">
-        <v>91613</v>
+        <v>80187</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5261,19 +5261,23 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr"/>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5281,10 +5285,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>444374</v>
+        <v>444511</v>
       </c>
       <c r="R47" t="n">
-        <v>7037756</v>
+        <v>7037681</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5330,7 +5334,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>Flerskiktad och olikåldrig grannaturskog</t>
+          <t>Friskt, örtrikt bäckdråg i grannaturskog</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -5348,10 +5352,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129562901</v>
+        <v>129562897</v>
       </c>
       <c r="B48" t="n">
-        <v>80187</v>
+        <v>91613</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5359,23 +5363,19 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5383,10 +5383,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>444511</v>
+        <v>444374</v>
       </c>
       <c r="R48" t="n">
-        <v>7037681</v>
+        <v>7037756</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Friskt, örtrikt bäckdråg i grannaturskog</t>
+          <t>Flerskiktad och olikåldrig grannaturskog</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -5552,10 +5552,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129562906</v>
+        <v>129562900</v>
       </c>
       <c r="B50" t="n">
-        <v>83050</v>
+        <v>80186</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5563,21 +5563,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5587,10 +5587,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>444395</v>
+        <v>444511</v>
       </c>
       <c r="R50" t="n">
-        <v>7037758</v>
+        <v>7037681</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5636,7 +5636,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Kalpåverkat fuktstråk</t>
+          <t>Friskt, örtrikt bäckdråg i grannaturskog</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -5654,10 +5654,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129562900</v>
+        <v>129562906</v>
       </c>
       <c r="B51" t="n">
-        <v>80186</v>
+        <v>83050</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5665,21 +5665,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5689,10 +5689,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>444511</v>
+        <v>444395</v>
       </c>
       <c r="R51" t="n">
-        <v>7037681</v>
+        <v>7037758</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>Friskt, örtrikt bäckdråg i grannaturskog</t>
+          <t>Kalpåverkat fuktstråk</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -5952,32 +5952,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129562898</v>
+        <v>129562899</v>
       </c>
       <c r="B54" t="n">
-        <v>79081</v>
+        <v>88841</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>4405</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5987,10 +5987,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>444587</v>
+        <v>444542</v>
       </c>
       <c r="R54" t="n">
-        <v>7037780</v>
+        <v>7037818</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6036,7 +6036,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>Flerskiktad och olikåldrig grannaturskog</t>
+          <t>Friskt, örtrikt bäckdråg i grannaturskog</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6054,32 +6054,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129562899</v>
+        <v>129562898</v>
       </c>
       <c r="B55" t="n">
-        <v>88841</v>
+        <v>79081</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4405</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6089,10 +6089,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>444542</v>
+        <v>444587</v>
       </c>
       <c r="R55" t="n">
-        <v>7037818</v>
+        <v>7037780</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>Friskt, örtrikt bäckdråg i grannaturskog</t>
+          <t>Flerskiktad och olikåldrig grannaturskog</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>

--- a/artfynd/A 30921-2025 artfynd.xlsx
+++ b/artfynd/A 30921-2025 artfynd.xlsx
@@ -5250,10 +5250,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129562901</v>
+        <v>129562897</v>
       </c>
       <c r="B47" t="n">
-        <v>80187</v>
+        <v>91613</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5261,23 +5261,19 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5285,10 +5281,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>444511</v>
+        <v>444374</v>
       </c>
       <c r="R47" t="n">
-        <v>7037681</v>
+        <v>7037756</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5334,7 +5330,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>Friskt, örtrikt bäckdråg i grannaturskog</t>
+          <t>Flerskiktad och olikåldrig grannaturskog</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -5352,10 +5348,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129562897</v>
+        <v>129562901</v>
       </c>
       <c r="B48" t="n">
-        <v>91613</v>
+        <v>80187</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5363,19 +5359,23 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5383,10 +5383,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>444374</v>
+        <v>444511</v>
       </c>
       <c r="R48" t="n">
-        <v>7037756</v>
+        <v>7037681</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Flerskiktad och olikåldrig grannaturskog</t>
+          <t>Friskt, örtrikt bäckdråg i grannaturskog</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -5552,10 +5552,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129562900</v>
+        <v>129562906</v>
       </c>
       <c r="B50" t="n">
-        <v>80186</v>
+        <v>83050</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5563,21 +5563,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5587,10 +5587,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>444511</v>
+        <v>444395</v>
       </c>
       <c r="R50" t="n">
-        <v>7037681</v>
+        <v>7037758</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5636,7 +5636,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Friskt, örtrikt bäckdråg i grannaturskog</t>
+          <t>Kalpåverkat fuktstråk</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -5654,10 +5654,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129562906</v>
+        <v>129562900</v>
       </c>
       <c r="B51" t="n">
-        <v>83050</v>
+        <v>80186</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5665,21 +5665,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5689,10 +5689,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>444395</v>
+        <v>444511</v>
       </c>
       <c r="R51" t="n">
-        <v>7037758</v>
+        <v>7037681</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>Kalpåverkat fuktstråk</t>
+          <t>Friskt, örtrikt bäckdråg i grannaturskog</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>

--- a/artfynd/A 30921-2025 artfynd.xlsx
+++ b/artfynd/A 30921-2025 artfynd.xlsx
@@ -5253,7 +5253,7 @@
         <v>129562897</v>
       </c>
       <c r="B47" t="n">
-        <v>91613</v>
+        <v>91617</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5453,7 +5453,7 @@
         <v>129562905</v>
       </c>
       <c r="B49" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         <v>129562903</v>
       </c>
       <c r="B52" t="n">
-        <v>91613</v>
+        <v>91617</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>129562896</v>
       </c>
       <c r="B53" t="n">
-        <v>91613</v>
+        <v>91617</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         <v>129562899</v>
       </c>
       <c r="B54" t="n">
-        <v>88841</v>
+        <v>88845</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 30921-2025 artfynd.xlsx
+++ b/artfynd/A 30921-2025 artfynd.xlsx
@@ -5253,7 +5253,7 @@
         <v>129562897</v>
       </c>
       <c r="B47" t="n">
-        <v>91617</v>
+        <v>91619</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5453,7 +5453,7 @@
         <v>129562905</v>
       </c>
       <c r="B49" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5552,10 +5552,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129562906</v>
+        <v>129562900</v>
       </c>
       <c r="B50" t="n">
-        <v>83050</v>
+        <v>80186</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5563,21 +5563,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5587,10 +5587,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>444395</v>
+        <v>444511</v>
       </c>
       <c r="R50" t="n">
-        <v>7037758</v>
+        <v>7037681</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5636,7 +5636,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Kalpåverkat fuktstråk</t>
+          <t>Friskt, örtrikt bäckdråg i grannaturskog</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -5654,10 +5654,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129562900</v>
+        <v>129562906</v>
       </c>
       <c r="B51" t="n">
-        <v>80186</v>
+        <v>83052</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5665,21 +5665,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5689,10 +5689,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>444511</v>
+        <v>444395</v>
       </c>
       <c r="R51" t="n">
-        <v>7037681</v>
+        <v>7037758</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>Friskt, örtrikt bäckdråg i grannaturskog</t>
+          <t>Kalpåverkat fuktstråk</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -5759,7 +5759,7 @@
         <v>129562903</v>
       </c>
       <c r="B52" t="n">
-        <v>91617</v>
+        <v>91619</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>129562896</v>
       </c>
       <c r="B53" t="n">
-        <v>91617</v>
+        <v>91619</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5952,32 +5952,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129562899</v>
+        <v>129562898</v>
       </c>
       <c r="B54" t="n">
-        <v>88845</v>
+        <v>79081</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4405</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5987,10 +5987,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>444542</v>
+        <v>444587</v>
       </c>
       <c r="R54" t="n">
-        <v>7037818</v>
+        <v>7037780</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6036,7 +6036,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>Friskt, örtrikt bäckdråg i grannaturskog</t>
+          <t>Flerskiktad och olikåldrig grannaturskog</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6054,32 +6054,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129562898</v>
+        <v>129562899</v>
       </c>
       <c r="B55" t="n">
-        <v>79081</v>
+        <v>88847</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>4405</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6089,10 +6089,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>444587</v>
+        <v>444542</v>
       </c>
       <c r="R55" t="n">
-        <v>7037780</v>
+        <v>7037818</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>Flerskiktad och olikåldrig grannaturskog</t>
+          <t>Friskt, örtrikt bäckdråg i grannaturskog</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>

--- a/artfynd/A 30921-2025 artfynd.xlsx
+++ b/artfynd/A 30921-2025 artfynd.xlsx
@@ -5450,10 +5450,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129562905</v>
+        <v>129562900</v>
       </c>
       <c r="B49" t="n">
-        <v>91599</v>
+        <v>80186</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5461,21 +5461,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5485,10 +5485,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>444381</v>
+        <v>444511</v>
       </c>
       <c r="R49" t="n">
-        <v>7037739</v>
+        <v>7037681</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5534,7 +5534,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>Kalpåverkat fuktstråk</t>
+          <t>Friskt, örtrikt bäckdråg i grannaturskog</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -5552,10 +5552,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129562900</v>
+        <v>129562903</v>
       </c>
       <c r="B50" t="n">
-        <v>80186</v>
+        <v>91619</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5563,23 +5563,19 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -5587,10 +5583,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>444511</v>
+        <v>444354</v>
       </c>
       <c r="R50" t="n">
-        <v>7037681</v>
+        <v>7037634</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5636,7 +5632,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Friskt, örtrikt bäckdråg i grannaturskog</t>
+          <t>Flerskiktad och olikåldrig grannaturskog</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -5654,10 +5650,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129562906</v>
+        <v>129562896</v>
       </c>
       <c r="B51" t="n">
-        <v>83052</v>
+        <v>91619</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5665,23 +5661,19 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -5689,10 +5681,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>444395</v>
+        <v>444598</v>
       </c>
       <c r="R51" t="n">
-        <v>7037758</v>
+        <v>7037765</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5738,7 +5730,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>Kalpåverkat fuktstråk</t>
+          <t>Flerskiktad och olikåldrig grannaturskog</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -5756,10 +5748,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129562903</v>
+        <v>129562898</v>
       </c>
       <c r="B52" t="n">
-        <v>91619</v>
+        <v>79081</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5767,19 +5759,23 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -5787,10 +5783,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>444354</v>
+        <v>444587</v>
       </c>
       <c r="R52" t="n">
-        <v>7037634</v>
+        <v>7037780</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5854,30 +5850,34 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129562896</v>
+        <v>129562899</v>
       </c>
       <c r="B53" t="n">
-        <v>91619</v>
+        <v>88847</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5432</v>
+        <v>4405</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
+          <t>Hygrophorus discoideus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Pers.) Fr.</t>
+        </is>
+      </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -5885,10 +5885,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>444598</v>
+        <v>444542</v>
       </c>
       <c r="R53" t="n">
-        <v>7037765</v>
+        <v>7037818</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5934,7 +5934,7 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>Flerskiktad och olikåldrig grannaturskog</t>
+          <t>Friskt, örtrikt bäckdråg i grannaturskog</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -5952,10 +5952,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129562898</v>
+        <v>129562905</v>
       </c>
       <c r="B54" t="n">
-        <v>79081</v>
+        <v>91599</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5963,34 +5963,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Naturskog söder om Kaxås, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>444587</v>
+        <v>444381</v>
       </c>
       <c r="R54" t="n">
-        <v>7037780</v>
+        <v>7037739</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6031,12 +6034,13 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>Flerskiktad och olikåldrig grannaturskog</t>
+          <t>Kalkpåverkat fuktstråk</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6054,45 +6058,48 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129562899</v>
+        <v>129562906</v>
       </c>
       <c r="B55" t="n">
-        <v>88847</v>
+        <v>83052</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4405</v>
+        <v>6440</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Naturskog söder om Kaxås, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>444542</v>
+        <v>444395</v>
       </c>
       <c r="R55" t="n">
-        <v>7037818</v>
+        <v>7037758</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6133,12 +6140,13 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>Friskt, örtrikt bäckdråg i grannaturskog</t>
+          <t>Kalkpåverkat fuktstråk</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>

--- a/artfynd/A 30921-2025 artfynd.xlsx
+++ b/artfynd/A 30921-2025 artfynd.xlsx
@@ -5250,10 +5250,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129562897</v>
+        <v>129562901</v>
       </c>
       <c r="B47" t="n">
-        <v>91619</v>
+        <v>80187</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5261,19 +5261,23 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr"/>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5281,10 +5285,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>444374</v>
+        <v>444511</v>
       </c>
       <c r="R47" t="n">
-        <v>7037756</v>
+        <v>7037681</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5330,7 +5334,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>Flerskiktad och olikåldrig grannaturskog</t>
+          <t>Friskt, örtrikt bäckdråg i grannaturskog</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -5348,10 +5352,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129562901</v>
+        <v>129562897</v>
       </c>
       <c r="B48" t="n">
-        <v>80187</v>
+        <v>91619</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5359,23 +5363,19 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5383,10 +5383,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>444511</v>
+        <v>444374</v>
       </c>
       <c r="R48" t="n">
-        <v>7037681</v>
+        <v>7037756</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Friskt, örtrikt bäckdråg i grannaturskog</t>
+          <t>Flerskiktad och olikåldrig grannaturskog</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -5748,32 +5748,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129562898</v>
+        <v>129562899</v>
       </c>
       <c r="B52" t="n">
-        <v>79081</v>
+        <v>88847</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>4405</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5783,10 +5783,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>444587</v>
+        <v>444542</v>
       </c>
       <c r="R52" t="n">
-        <v>7037780</v>
+        <v>7037818</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5832,7 +5832,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>Flerskiktad och olikåldrig grannaturskog</t>
+          <t>Friskt, örtrikt bäckdråg i grannaturskog</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -5850,32 +5850,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129562899</v>
+        <v>129562898</v>
       </c>
       <c r="B53" t="n">
-        <v>88847</v>
+        <v>79081</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4405</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5885,10 +5885,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>444542</v>
+        <v>444587</v>
       </c>
       <c r="R53" t="n">
-        <v>7037818</v>
+        <v>7037780</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5934,7 +5934,7 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>Friskt, örtrikt bäckdråg i grannaturskog</t>
+          <t>Flerskiktad och olikåldrig grannaturskog</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>

--- a/artfynd/A 30921-2025 artfynd.xlsx
+++ b/artfynd/A 30921-2025 artfynd.xlsx
@@ -5250,10 +5250,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129562901</v>
+        <v>129562897</v>
       </c>
       <c r="B47" t="n">
-        <v>80187</v>
+        <v>91619</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5261,23 +5261,19 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5285,10 +5281,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>444511</v>
+        <v>444374</v>
       </c>
       <c r="R47" t="n">
-        <v>7037681</v>
+        <v>7037756</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5334,7 +5330,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>Friskt, örtrikt bäckdråg i grannaturskog</t>
+          <t>Flerskiktad och olikåldrig grannaturskog</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -5352,10 +5348,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129562897</v>
+        <v>129562901</v>
       </c>
       <c r="B48" t="n">
-        <v>91619</v>
+        <v>80187</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5363,19 +5359,23 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5383,10 +5383,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>444374</v>
+        <v>444511</v>
       </c>
       <c r="R48" t="n">
-        <v>7037756</v>
+        <v>7037681</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Flerskiktad och olikåldrig grannaturskog</t>
+          <t>Friskt, örtrikt bäckdråg i grannaturskog</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>

--- a/artfynd/A 30921-2025 artfynd.xlsx
+++ b/artfynd/A 30921-2025 artfynd.xlsx
@@ -5955,7 +5955,7 @@
         <v>129562905</v>
       </c>
       <c r="B54" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6061,7 +6061,7 @@
         <v>129562906</v>
       </c>
       <c r="B55" t="n">
-        <v>83052</v>
+        <v>83055</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 30921-2025 artfynd.xlsx
+++ b/artfynd/A 30921-2025 artfynd.xlsx
@@ -5253,7 +5253,7 @@
         <v>129562897</v>
       </c>
       <c r="B47" t="n">
-        <v>91619</v>
+        <v>91622</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         <v>129562901</v>
       </c>
       <c r="B48" t="n">
-        <v>80187</v>
+        <v>80190</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5453,7 +5453,7 @@
         <v>129562900</v>
       </c>
       <c r="B49" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>129562903</v>
       </c>
       <c r="B50" t="n">
-        <v>91619</v>
+        <v>91622</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5653,7 +5653,7 @@
         <v>129562896</v>
       </c>
       <c r="B51" t="n">
-        <v>91619</v>
+        <v>91622</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5751,7 +5751,7 @@
         <v>129562899</v>
       </c>
       <c r="B52" t="n">
-        <v>88847</v>
+        <v>88850</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5853,7 +5853,7 @@
         <v>129562898</v>
       </c>
       <c r="B53" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 30921-2025 artfynd.xlsx
+++ b/artfynd/A 30921-2025 artfynd.xlsx
@@ -5955,7 +5955,7 @@
         <v>129562905</v>
       </c>
       <c r="B54" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6061,7 +6061,7 @@
         <v>129562906</v>
       </c>
       <c r="B55" t="n">
-        <v>83055</v>
+        <v>83058</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
